--- a/单词发音解析.xlsx
+++ b/单词发音解析.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rr/github_repo/EnglishSummary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02532E57-E0DD-CF41-94E9-FC21EE52FD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0445F9BF-0359-CB46-A748-257AFA4D1945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="1440" windowWidth="23100" windowHeight="13480" tabRatio="708" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3100" yWindow="1420" windowWidth="23100" windowHeight="13480" tabRatio="708" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普遍重音规律" sheetId="8" r:id="rId1"/>
@@ -19,32 +19,33 @@
     <sheet name="规律" sheetId="30" r:id="rId4"/>
     <sheet name="特殊音变" sheetId="32" r:id="rId5"/>
     <sheet name="词间连读" sheetId="10" r:id="rId6"/>
-    <sheet name="听不出单词" sheetId="36" r:id="rId7"/>
-    <sheet name="常见易发错" sheetId="37" r:id="rId8"/>
-    <sheet name="A" sheetId="1" r:id="rId9"/>
-    <sheet name="B" sheetId="2" r:id="rId10"/>
-    <sheet name="C" sheetId="11" r:id="rId11"/>
-    <sheet name="D" sheetId="3" r:id="rId12"/>
-    <sheet name="E" sheetId="14" r:id="rId13"/>
-    <sheet name="F" sheetId="15" r:id="rId14"/>
-    <sheet name="G" sheetId="24" r:id="rId15"/>
-    <sheet name="H" sheetId="23" r:id="rId16"/>
-    <sheet name="I" sheetId="22" r:id="rId17"/>
-    <sheet name="J" sheetId="27" r:id="rId18"/>
-    <sheet name="K" sheetId="31" r:id="rId19"/>
-    <sheet name="L" sheetId="25" r:id="rId20"/>
-    <sheet name="M" sheetId="9" r:id="rId21"/>
-    <sheet name="N" sheetId="17" r:id="rId22"/>
-    <sheet name="O" sheetId="12" r:id="rId23"/>
-    <sheet name="P" sheetId="18" r:id="rId24"/>
-    <sheet name="Q" sheetId="28" r:id="rId25"/>
-    <sheet name="R" sheetId="16" r:id="rId26"/>
-    <sheet name="S" sheetId="7" r:id="rId27"/>
-    <sheet name="T" sheetId="5" r:id="rId28"/>
-    <sheet name="U" sheetId="33" r:id="rId29"/>
-    <sheet name="V" sheetId="13" r:id="rId30"/>
-    <sheet name="W" sheetId="26" r:id="rId31"/>
-    <sheet name="Y" sheetId="35" r:id="rId32"/>
+    <sheet name="ou aw的几个发音" sheetId="38" r:id="rId7"/>
+    <sheet name="听不出单词" sheetId="36" r:id="rId8"/>
+    <sheet name="RA常见易发错" sheetId="37" r:id="rId9"/>
+    <sheet name="A" sheetId="1" r:id="rId10"/>
+    <sheet name="B" sheetId="2" r:id="rId11"/>
+    <sheet name="C" sheetId="11" r:id="rId12"/>
+    <sheet name="D" sheetId="3" r:id="rId13"/>
+    <sheet name="E" sheetId="14" r:id="rId14"/>
+    <sheet name="F" sheetId="15" r:id="rId15"/>
+    <sheet name="G" sheetId="24" r:id="rId16"/>
+    <sheet name="H" sheetId="23" r:id="rId17"/>
+    <sheet name="I" sheetId="22" r:id="rId18"/>
+    <sheet name="J" sheetId="27" r:id="rId19"/>
+    <sheet name="K" sheetId="31" r:id="rId20"/>
+    <sheet name="L" sheetId="25" r:id="rId21"/>
+    <sheet name="M" sheetId="9" r:id="rId22"/>
+    <sheet name="N" sheetId="17" r:id="rId23"/>
+    <sheet name="O" sheetId="12" r:id="rId24"/>
+    <sheet name="P" sheetId="18" r:id="rId25"/>
+    <sheet name="Q" sheetId="28" r:id="rId26"/>
+    <sheet name="R" sheetId="16" r:id="rId27"/>
+    <sheet name="S" sheetId="7" r:id="rId28"/>
+    <sheet name="T" sheetId="5" r:id="rId29"/>
+    <sheet name="U" sheetId="33" r:id="rId30"/>
+    <sheet name="V" sheetId="13" r:id="rId31"/>
+    <sheet name="W" sheetId="26" r:id="rId32"/>
+    <sheet name="Y" sheetId="35" r:id="rId33"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="2279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="2371">
   <si>
     <t>音标</t>
   </si>
@@ -7781,6 +7782,9 @@
     <t>/ˈrɪt(ə)n/</t>
   </si>
   <si>
+    <t>/ˌækəˈdemɪk/</t>
+  </si>
+  <si>
     <r>
       <t>/ˌ</t>
     </r>
@@ -7819,14 +7823,749 @@
     <t>object</t>
   </si>
   <si>
-    <t>/ˈɑːbdʒekt/</t>
+    <t>example</t>
+  </si>
+  <si>
+    <r>
+      <t>/ɪɡˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>zæ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mp(ə)l/</t>
+    </r>
+  </si>
+  <si>
+    <t>lack</t>
+  </si>
+  <si>
+    <t>/læk/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland </t>
+  </si>
+  <si>
+    <t xml:space="preserve">/ˈswɪ  ts= cə  rlənd/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">evolve </t>
+  </si>
+  <si>
+    <t>/ˌiːvəˈluːʃ(ə)n/  美音 e</t>
+  </si>
+  <si>
+    <t>consequence</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ˈkɑːnsɪk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wens/</t>
+    </r>
+  </si>
+  <si>
+    <t>possess</t>
+  </si>
+  <si>
+    <r>
+      <t>/pəˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>zes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
+    <t>/ˈtrɪɡər/</t>
+  </si>
+  <si>
+    <r>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ˈemɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ɡrənt/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/ɪmˈpɔː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>r nt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+  </si>
+  <si>
+    <t>explanation</t>
+  </si>
+  <si>
+    <r>
+      <t>/ˌeks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>plə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ˈneɪʃ(ə)n/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>eɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ʃə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n</t>
+    </r>
+  </si>
+  <si>
+    <t>accessible</t>
+  </si>
+  <si>
+    <t>embryonic</t>
+  </si>
+  <si>
+    <t>ˌembriˈ</t>
+  </si>
+  <si>
+    <t>particulate</t>
+  </si>
+  <si>
+    <t>almond</t>
+  </si>
+  <si>
+    <r>
+      <t>/pɑːrˈtɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>kjələ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t/</t>
+    </r>
+  </si>
+  <si>
+    <t>/ˈɑːmənd/</t>
+  </si>
+  <si>
+    <t>‘---zation</t>
+  </si>
+  <si>
+    <t>zeiii ʃən</t>
+  </si>
+  <si>
+    <t>rather</t>
+  </si>
+  <si>
+    <t>stabilze</t>
+  </si>
+  <si>
+    <r>
+      <t>/ˈst</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>eɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bəlaɪz</t>
+    </r>
+  </si>
+  <si>
+    <t>idea</t>
+  </si>
+  <si>
+    <r>
+      <t>/a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ɪˈdiːə/</t>
+    </r>
+  </si>
+  <si>
+    <t>/ˈɑːbdʒe --  t/</t>
+  </si>
+  <si>
+    <t>the impact of the</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ði  ˈɪmpæ--t  / of the</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>/ɪkˈstɜːrn(ə)l</t>
+  </si>
+  <si>
+    <t>/kəmˈpærɪsn/</t>
+  </si>
+  <si>
+    <t>comparable</t>
+  </si>
+  <si>
+    <t>注意重音前移，able结尾算一个音节，到三原则</t>
+  </si>
+  <si>
+    <r>
+      <t>/ˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>kɑːm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pərəb(ə)l/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>siːk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rət/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/ɔː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">str </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>sdr e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ɪliə/</t>
+    </r>
+  </si>
+  <si>
+    <t>ɒ</t>
+  </si>
+  <si>
+    <t>ʌ</t>
+  </si>
+  <si>
+    <t>ɑː</t>
+  </si>
+  <si>
+    <t>aʊn</t>
+  </si>
+  <si>
+    <t>常见拼写</t>
+  </si>
+  <si>
+    <t>un</t>
+  </si>
+  <si>
+    <t>fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘴型不懂，喉咙发音 a 向下低沉的发音， </t>
+  </si>
+  <si>
+    <t>与n 结合时说明</t>
+  </si>
+  <si>
+    <t>æ</t>
+  </si>
+  <si>
+    <t>通过喉咙发an的音 ʌ-n</t>
+  </si>
+  <si>
+    <t>与ʌ的区别，梅花音是靠口腔前部发音 ，通过and的发音，区别ʌn的</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>发音位置与ʌ 相同， 但是口腔前部要张大，并且发音时间较长</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ar </t>
+  </si>
+  <si>
+    <t>英式音标的 ɔ ， 发短促‘喔’的音，</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aw </t>
+  </si>
+  <si>
+    <t>law， drawn</t>
+  </si>
+  <si>
+    <t>oun， own</t>
+  </si>
+  <si>
+    <t>舌根后缩，喉部发音，嘴型收圆，声音向下低沉， 因发音位置与ɑː 相同，所以很多美音， 将其发成 ɑː</t>
+  </si>
+  <si>
+    <t>正解是au -n 组合发音， 但是有时可以直接使用 ang ‘昂n' 代替发音。，但要注意区别， ang 发音时舌位在口腔下方， ang-n，舌头最后要顶上去，有n的发音</t>
+  </si>
+  <si>
+    <t>down ， found</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ˈprɑ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ːses 、/ˈprəʊses</t>
+    </r>
+  </si>
+  <si>
+    <t>influence</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>‘ɪn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fluəns/</t>
+    </r>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">/sə </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ˈmɪt</t>
+    </r>
+  </si>
+  <si>
+    <t>we see(k)升调 to improve 降调</t>
+  </si>
+  <si>
+    <r>
+      <t>/əkˈse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>sə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b(ə)l/</t>
+    </r>
+  </si>
+  <si>
+    <t>associate</t>
+  </si>
+  <si>
+    <t>两个读音都可以，尽量使用si</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>/ə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ˈs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>oʊSiɪt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> əˈsoʊʃieɪt/</t>
+    </r>
+  </si>
+  <si>
+    <t>globalization</t>
+  </si>
+  <si>
+    <r>
+      <t>/ˌɡləʊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>bə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>laɪˈzeɪʃn/</t>
+    </r>
+  </si>
+  <si>
+    <t>注意是 bə ， 没有bəl 后l的音</t>
+  </si>
+  <si>
+    <r>
+      <t>/ˈræ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ðər</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+  </si>
+  <si>
+    <t>注意 咬舌发音</t>
+  </si>
+  <si>
+    <t>daught</t>
+  </si>
+  <si>
+    <t>ˈdɔːtər/</t>
+  </si>
+  <si>
+    <r>
+      <t>/ɑːmˈnɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ʃəns/</t>
+    </r>
+  </si>
+  <si>
+    <t>science 做词根 发 ʃəns/</t>
+  </si>
+  <si>
+    <t>graudate</t>
+  </si>
+  <si>
+    <r>
+      <t>/ˈɡrædʒu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>ə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+  </si>
+  <si>
+    <t>结尾是ət 不是eit</t>
+  </si>
+  <si>
+    <t>ge --ges</t>
+  </si>
+  <si>
+    <t>dʒ --&gt;dʒɪz</t>
+  </si>
+  <si>
+    <t>mature</t>
+  </si>
+  <si>
+    <r>
+      <t>/m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>əˈt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ʃʊr/</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7933,6 +8672,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -7954,7 +8704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -8093,6 +8843,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9029,6 +9782,428 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="E3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="D4" t="s">
+        <v>534</v>
+      </c>
+      <c r="E4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C6" t="s">
+        <v>544</v>
+      </c>
+      <c r="D6" t="s">
+        <v>546</v>
+      </c>
+      <c r="E6" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>584</v>
+      </c>
+      <c r="C7" t="s">
+        <v>585</v>
+      </c>
+      <c r="E7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>583</v>
+      </c>
+      <c r="C8" t="s">
+        <v>587</v>
+      </c>
+      <c r="D8" t="s">
+        <v>589</v>
+      </c>
+      <c r="E8" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>915</v>
+      </c>
+      <c r="C9" t="s">
+        <v>916</v>
+      </c>
+      <c r="D9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="29" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="29" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>429</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="3" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>799</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9221,7 +10396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9956,7 +11131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10254,7 +11429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10516,7 +11691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10666,7 +11841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10826,7 +12001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10959,7 +12134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -11203,7 +12378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -11254,61 +12429,6 @@
       </c>
       <c r="G2" t="s">
         <v>854</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="61.1640625" customWidth="1"/>
-    <col min="5" max="8" width="15.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1375</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1374</v>
       </c>
     </row>
   </sheetData>
@@ -13101,6 +14221,61 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="61.1640625" customWidth="1"/>
+    <col min="5" max="8" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13218,7 +14393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13475,7 +14650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13565,7 +14740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13815,7 +14990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -14171,7 +15346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -14251,7 +15426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -14437,7 +15612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -14864,7 +16039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15247,62 +16422,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D136FC-C914-D441-87B5-9A5195970599}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="8" width="17" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>1698</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1699</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1700</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1701</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -17342,6 +18461,62 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D136FC-C914-D441-87B5-9A5195970599}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="8" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -17448,7 +18623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -17521,7 +18696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01711787-A543-CD4C-BD80-9488CE8FC5C6}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -19020,6 +20195,118 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3276CE1D-178D-B644-B729-C24FBFCF3ECF}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="53" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="53" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="53" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="53" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E6613A-B6DC-1A40-9B6C-B1C6AC3A5DD8}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -19145,9 +20432,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E5FF9F3-56C9-3748-85E0-50DFD7DC9EB7}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -19234,10 +20521,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B9" t="s">
         <v>2273</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2272</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -19245,448 +20532,342 @@
         <v>1364</v>
       </c>
       <c r="B10" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="B12" t="s">
-        <v>2278</v>
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>959</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>2370</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F2" t="s">
-        <v>360</v>
-      </c>
-      <c r="G2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="E3" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="D4" t="s">
-        <v>534</v>
-      </c>
-      <c r="E4" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>540</v>
-      </c>
-      <c r="C5" t="s">
-        <v>541</v>
-      </c>
-      <c r="D5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>543</v>
-      </c>
-      <c r="C6" t="s">
-        <v>544</v>
-      </c>
-      <c r="D6" t="s">
-        <v>546</v>
-      </c>
-      <c r="E6" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>584</v>
-      </c>
-      <c r="C7" t="s">
-        <v>585</v>
-      </c>
-      <c r="E7" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>583</v>
-      </c>
-      <c r="C8" t="s">
-        <v>587</v>
-      </c>
-      <c r="D8" t="s">
-        <v>589</v>
-      </c>
-      <c r="E8" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>915</v>
-      </c>
-      <c r="C9" t="s">
-        <v>916</v>
-      </c>
-      <c r="D9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="29" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="29" t="s">
-        <v>1389</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>1519</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>2130</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2131</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2132</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>2134</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>2136</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2137</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>2139</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2140</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>2142</v>
-      </c>
-      <c r="C24" t="s">
-        <v>429</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>2144</v>
-      </c>
-      <c r="C25" t="s">
-        <v>2145</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>2147</v>
-      </c>
-      <c r="C26" t="s">
-        <v>2149</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>1596</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1597</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1600</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F40" t="s">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>1618</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1619</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D43" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" s="3" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>1935</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>1932</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>799</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1955</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>1957</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>1959</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>1964</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>